--- a/grupos/4BEM - Estadisticos 20232.xlsx
+++ b/grupos/4BEM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="87">
   <si>
     <t>Materia</t>
   </si>
@@ -194,18 +194,18 @@
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
+    <t>Faltante Faltante Faltante</t>
+  </si>
+  <si>
+    <t>Hernández Castro Enrique</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>Hernández Castro Enrique</t>
-  </si>
-  <si>
-    <t>Faltante Faltante Faltante</t>
-  </si>
-  <si>
     <t>Flores Paz Victor</t>
   </si>
   <si>
@@ -224,33 +224,18 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>PALOMINO</t>
+  </si>
+  <si>
     <t>GIL</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JENKINS</t>
-  </si>
-  <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>MELCHOR</t>
   </si>
   <si>
-    <t>PALESTINO</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -263,27 +248,12 @@
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>MENDOZA</t>
   </si>
   <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>LOMAS</t>
-  </si>
-  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
@@ -293,31 +263,16 @@
     <t>CARLOS YAEL</t>
   </si>
   <si>
+    <t>AARON MIGUEL</t>
+  </si>
+  <si>
     <t>JOSE RAUL</t>
   </si>
   <si>
-    <t>MIGUEL ANTONIO</t>
-  </si>
-  <si>
-    <t>ARTHUR RICHARD</t>
-  </si>
-  <si>
-    <t>AARON MIGUEL</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
     <t>DAMIAN</t>
   </si>
   <si>
     <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>GUILLERMO JESUS</t>
   </si>
   <si>
     <t>JORGE IVAN</t>
@@ -850,25 +805,25 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -892,19 +847,19 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z4">
         <v>10</v>
       </c>
       <c r="AA4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB4">
         <v>8</v>
@@ -939,25 +894,25 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -996,7 +951,7 @@
         <v>10</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC5">
         <v>10</v>
@@ -1028,25 +983,25 @@
         <v>6</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1070,22 +1025,22 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC6">
         <v>6</v>
@@ -1111,31 +1066,31 @@
         <v>9</v>
       </c>
       <c r="G7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H7">
         <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1159,19 +1114,19 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB7">
         <v>9</v>
@@ -1206,25 +1161,25 @@
         <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1289,31 +1244,31 @@
         <v>7</v>
       </c>
       <c r="G9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H9">
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1340,16 +1295,16 @@
         <v>7</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z9">
         <v>10</v>
       </c>
       <c r="AA9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB9">
         <v>7</v>
@@ -1378,31 +1333,31 @@
         <v>8</v>
       </c>
       <c r="G10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10">
         <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1432,7 +1387,7 @@
         <v>7</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z10">
         <v>5</v>
@@ -1467,31 +1422,31 @@
         <v>8</v>
       </c>
       <c r="G11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H11">
         <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1521,16 +1476,16 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z11">
         <v>7</v>
       </c>
       <c r="AA11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC11">
         <v>10</v>
@@ -1556,31 +1511,31 @@
         <v>8</v>
       </c>
       <c r="G12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H12">
         <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1604,25 +1559,25 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>8</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA12">
         <v>8</v>
       </c>
       <c r="AB12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1651,25 +1606,25 @@
         <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1696,7 +1651,7 @@
         <v>5</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>8</v>
@@ -1705,13 +1660,13 @@
         <v>7</v>
       </c>
       <c r="AA13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC13">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1734,31 +1689,31 @@
         <v>8</v>
       </c>
       <c r="G14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H14">
         <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1785,10 +1740,10 @@
         <v>6</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z14">
         <v>8</v>
@@ -1800,7 +1755,7 @@
         <v>8</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1823,31 +1778,31 @@
         <v>8</v>
       </c>
       <c r="G15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H15">
         <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1874,19 +1829,19 @@
         <v>5</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA15">
         <v>8</v>
       </c>
       <c r="AB15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC15">
         <v>7</v>
@@ -1918,25 +1873,25 @@
         <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1963,10 +1918,10 @@
         <v>5</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z16">
         <v>5</v>
@@ -1975,7 +1930,7 @@
         <v>6</v>
       </c>
       <c r="AB16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC16">
         <v>6</v>
@@ -2001,31 +1956,31 @@
         <v>8</v>
       </c>
       <c r="G17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H17">
         <v>5</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2055,16 +2010,16 @@
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC17">
         <v>5</v>
@@ -2090,31 +2045,31 @@
         <v>8</v>
       </c>
       <c r="G18">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H18">
         <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2138,10 +2093,10 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>8</v>
@@ -2153,10 +2108,10 @@
         <v>8</v>
       </c>
       <c r="AB18">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2179,31 +2134,31 @@
         <v>7</v>
       </c>
       <c r="G19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H19">
         <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2230,13 +2185,13 @@
         <v>5</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA19">
         <v>7</v>
@@ -2245,7 +2200,7 @@
         <v>7</v>
       </c>
       <c r="AC19">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2268,31 +2223,31 @@
         <v>9</v>
       </c>
       <c r="G20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H20">
         <v>8</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2316,25 +2271,25 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y20">
         <v>10</v>
       </c>
       <c r="Z20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC20">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2363,25 +2318,25 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2405,22 +2360,22 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z21">
         <v>7</v>
       </c>
       <c r="AA21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>8</v>
@@ -2446,31 +2401,31 @@
         <v>8</v>
       </c>
       <c r="G22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H22">
         <v>7</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2497,10 +2452,10 @@
         <v>5</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z22">
         <v>5</v>
@@ -2509,10 +2464,10 @@
         <v>8</v>
       </c>
       <c r="AB22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC22">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2535,31 +2490,31 @@
         <v>9</v>
       </c>
       <c r="G23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H23">
         <v>7</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2586,10 +2541,10 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z23">
         <v>7</v>
@@ -2598,7 +2553,7 @@
         <v>9</v>
       </c>
       <c r="AB23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC23">
         <v>7</v>
@@ -2624,31 +2579,31 @@
         <v>9</v>
       </c>
       <c r="G24">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H24">
         <v>5</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2675,19 +2630,19 @@
         <v>5</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z24">
         <v>6</v>
       </c>
       <c r="AA24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB24">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC24">
         <v>5</v>
@@ -2713,31 +2668,31 @@
         <v>8</v>
       </c>
       <c r="G25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H25">
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2761,7 +2716,7 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>8</v>
@@ -2770,13 +2725,13 @@
         <v>9</v>
       </c>
       <c r="Z25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA25">
         <v>8</v>
       </c>
       <c r="AB25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC25">
         <v>10</v>
@@ -2802,31 +2757,31 @@
         <v>7</v>
       </c>
       <c r="G26">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H26">
         <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2856,16 +2811,16 @@
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z26">
         <v>10</v>
       </c>
       <c r="AA26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC26">
         <v>9</v>
@@ -2891,31 +2846,31 @@
         <v>8</v>
       </c>
       <c r="G27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H27">
         <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2939,22 +2894,22 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC27">
         <v>9</v>
@@ -2980,31 +2935,31 @@
         <v>9</v>
       </c>
       <c r="G28">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H28">
         <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3031,19 +2986,19 @@
         <v>6</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA28">
         <v>9</v>
       </c>
       <c r="AB28">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC28">
         <v>7</v>
@@ -3069,31 +3024,31 @@
         <v>8</v>
       </c>
       <c r="G29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H29">
         <v>8</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3120,10 +3075,10 @@
         <v>6</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z29">
         <v>7</v>
@@ -3135,7 +3090,7 @@
         <v>8</v>
       </c>
       <c r="AC29">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3164,25 +3119,25 @@
         <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3212,16 +3167,16 @@
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC30">
         <v>10</v>
@@ -3253,25 +3208,25 @@
         <v>6</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3307,10 +3262,10 @@
         <v>5</v>
       </c>
       <c r="AA31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC31">
         <v>6</v>
@@ -3336,31 +3291,31 @@
         <v>9</v>
       </c>
       <c r="G32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H32">
         <v>8</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3390,19 +3345,19 @@
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA32">
         <v>9</v>
       </c>
       <c r="AB32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC32">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3425,31 +3380,31 @@
         <v>8</v>
       </c>
       <c r="G33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H33">
         <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3473,13 +3428,13 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z33">
         <v>10</v>
@@ -3520,25 +3475,25 @@
         <v>9</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3568,7 +3523,7 @@
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z34">
         <v>10</v>
@@ -3577,10 +3532,10 @@
         <v>9</v>
       </c>
       <c r="AB34">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC34">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3873,13 +3828,13 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="L6">
         <v>100</v>
       </c>
       <c r="M6">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="N6">
         <v>100</v>
@@ -3894,13 +3849,13 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="S6">
         <v>100</v>
       </c>
       <c r="T6">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="U6">
         <v>100</v>
@@ -3947,7 +3902,7 @@
         <v>100</v>
       </c>
       <c r="M7">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="N7">
         <v>100</v>
@@ -3968,7 +3923,7 @@
         <v>100</v>
       </c>
       <c r="T7">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="U7">
         <v>100</v>
@@ -4083,7 +4038,7 @@
         <v>100</v>
       </c>
       <c r="M9">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="N9">
         <v>100</v>
@@ -4104,7 +4059,7 @@
         <v>100</v>
       </c>
       <c r="T9">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="U9">
         <v>100</v>
@@ -4151,7 +4106,7 @@
         <v>100</v>
       </c>
       <c r="M10">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="N10">
         <v>100</v>
@@ -4172,7 +4127,7 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="U10">
         <v>100</v>
@@ -4207,19 +4162,19 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J11">
         <v>100</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L11">
         <v>100</v>
       </c>
       <c r="M11">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="N11">
         <v>100</v>
@@ -4228,19 +4183,19 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q11">
         <v>100</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S11">
         <v>100</v>
       </c>
       <c r="T11">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="U11">
         <v>100</v>
@@ -4275,7 +4230,7 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -4287,7 +4242,7 @@
         <v>100</v>
       </c>
       <c r="M12">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="N12">
         <v>100</v>
@@ -4296,7 +4251,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -4308,7 +4263,7 @@
         <v>100</v>
       </c>
       <c r="T12">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="U12">
         <v>100</v>
@@ -4343,7 +4298,7 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J13">
         <v>100</v>
@@ -4355,7 +4310,7 @@
         <v>100</v>
       </c>
       <c r="M13">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="N13">
         <v>100</v>
@@ -4364,7 +4319,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -4376,7 +4331,7 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -4423,7 +4378,7 @@
         <v>100</v>
       </c>
       <c r="M14">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="N14">
         <v>100</v>
@@ -4444,7 +4399,7 @@
         <v>100</v>
       </c>
       <c r="T14">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="U14">
         <v>100</v>
@@ -4485,7 +4440,7 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L15">
         <v>100</v>
@@ -4506,7 +4461,7 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -4553,13 +4508,13 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="L16">
         <v>100</v>
       </c>
       <c r="M16">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N16">
         <v>100</v>
@@ -4574,13 +4529,13 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="S16">
         <v>100</v>
       </c>
       <c r="T16">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -4621,13 +4576,13 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L17">
         <v>100</v>
       </c>
       <c r="M17">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N17">
         <v>100</v>
@@ -4642,13 +4597,13 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S17">
         <v>100</v>
       </c>
       <c r="T17">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="U17">
         <v>100</v>
@@ -4751,7 +4706,7 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J19">
         <v>100</v>
@@ -4763,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="M19">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="N19">
         <v>100</v>
@@ -4772,7 +4727,7 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -4784,7 +4739,7 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="U19">
         <v>100</v>
@@ -4899,7 +4854,7 @@
         <v>100</v>
       </c>
       <c r="M21">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="N21">
         <v>100</v>
@@ -4920,7 +4875,7 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="U21">
         <v>100</v>
@@ -4955,7 +4910,7 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J22">
         <v>100</v>
@@ -4967,7 +4922,7 @@
         <v>100</v>
       </c>
       <c r="M22">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N22">
         <v>100</v>
@@ -4976,7 +4931,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -4988,7 +4943,7 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="U22">
         <v>100</v>
@@ -5023,20 +4978,20 @@
         <v>100</v>
       </c>
       <c r="I23">
+        <v>87.5</v>
+      </c>
+      <c r="J23">
+        <v>100</v>
+      </c>
+      <c r="K23">
+        <v>95.5</v>
+      </c>
+      <c r="L23">
+        <v>100</v>
+      </c>
+      <c r="M23">
         <v>90</v>
       </c>
-      <c r="J23">
-        <v>100</v>
-      </c>
-      <c r="K23">
-        <v>91.7</v>
-      </c>
-      <c r="L23">
-        <v>100</v>
-      </c>
-      <c r="M23">
-        <v>100</v>
-      </c>
       <c r="N23">
         <v>100</v>
       </c>
@@ -5044,19 +4999,19 @@
         <v>100</v>
       </c>
       <c r="P23">
+        <v>87.5</v>
+      </c>
+      <c r="Q23">
+        <v>100</v>
+      </c>
+      <c r="R23">
+        <v>95.5</v>
+      </c>
+      <c r="S23">
+        <v>100</v>
+      </c>
+      <c r="T23">
         <v>90</v>
-      </c>
-      <c r="Q23">
-        <v>100</v>
-      </c>
-      <c r="R23">
-        <v>91.7</v>
-      </c>
-      <c r="S23">
-        <v>100</v>
-      </c>
-      <c r="T23">
-        <v>100</v>
       </c>
       <c r="U23">
         <v>100</v>
@@ -5091,19 +5046,19 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J24">
         <v>100</v>
       </c>
       <c r="K24">
-        <v>91.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L24">
         <v>100</v>
       </c>
       <c r="M24">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N24">
         <v>100</v>
@@ -5112,19 +5067,19 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q24">
         <v>100</v>
       </c>
       <c r="R24">
-        <v>91.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S24">
         <v>100</v>
       </c>
       <c r="T24">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="U24">
         <v>100</v>
@@ -5171,7 +5126,7 @@
         <v>100</v>
       </c>
       <c r="M25">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="N25">
         <v>100</v>
@@ -5192,7 +5147,7 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="U25">
         <v>100</v>
@@ -5307,7 +5262,7 @@
         <v>100</v>
       </c>
       <c r="M27">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="N27">
         <v>100</v>
@@ -5328,7 +5283,7 @@
         <v>100</v>
       </c>
       <c r="T27">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="U27">
         <v>100</v>
@@ -5363,7 +5318,7 @@
         <v>100</v>
       </c>
       <c r="I28">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J28">
         <v>100</v>
@@ -5375,7 +5330,7 @@
         <v>100</v>
       </c>
       <c r="M28">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="N28">
         <v>100</v>
@@ -5384,7 +5339,7 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -5396,7 +5351,7 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="U28">
         <v>100</v>
@@ -5443,7 +5398,7 @@
         <v>100</v>
       </c>
       <c r="M29">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="N29">
         <v>100</v>
@@ -5464,7 +5419,7 @@
         <v>100</v>
       </c>
       <c r="T29">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="U29">
         <v>100</v>
@@ -5499,7 +5454,7 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J30">
         <v>100</v>
@@ -5511,7 +5466,7 @@
         <v>100</v>
       </c>
       <c r="M30">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="N30">
         <v>100</v>
@@ -5520,7 +5475,7 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5532,7 +5487,7 @@
         <v>100</v>
       </c>
       <c r="T30">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="U30">
         <v>100</v>
@@ -5567,20 +5522,20 @@
         <v>100</v>
       </c>
       <c r="I31">
+        <v>85</v>
+      </c>
+      <c r="J31">
+        <v>100</v>
+      </c>
+      <c r="K31">
+        <v>95.5</v>
+      </c>
+      <c r="L31">
+        <v>100</v>
+      </c>
+      <c r="M31">
         <v>80</v>
       </c>
-      <c r="J31">
-        <v>100</v>
-      </c>
-      <c r="K31">
-        <v>91.7</v>
-      </c>
-      <c r="L31">
-        <v>100</v>
-      </c>
-      <c r="M31">
-        <v>100</v>
-      </c>
       <c r="N31">
         <v>100</v>
       </c>
@@ -5588,19 +5543,19 @@
         <v>100</v>
       </c>
       <c r="P31">
+        <v>85</v>
+      </c>
+      <c r="Q31">
+        <v>100</v>
+      </c>
+      <c r="R31">
+        <v>95.5</v>
+      </c>
+      <c r="S31">
+        <v>100</v>
+      </c>
+      <c r="T31">
         <v>80</v>
-      </c>
-      <c r="Q31">
-        <v>100</v>
-      </c>
-      <c r="R31">
-        <v>91.7</v>
-      </c>
-      <c r="S31">
-        <v>100</v>
-      </c>
-      <c r="T31">
-        <v>100</v>
       </c>
       <c r="U31">
         <v>100</v>
@@ -5647,7 +5602,7 @@
         <v>100</v>
       </c>
       <c r="M32">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N32">
         <v>100</v>
@@ -5668,7 +5623,7 @@
         <v>100</v>
       </c>
       <c r="T32">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="U32">
         <v>100</v>
@@ -5703,7 +5658,7 @@
         <v>100</v>
       </c>
       <c r="I33">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="J33">
         <v>100</v>
@@ -5715,7 +5670,7 @@
         <v>100</v>
       </c>
       <c r="M33">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="N33">
         <v>100</v>
@@ -5724,7 +5679,7 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="Q33">
         <v>100</v>
@@ -5736,7 +5691,7 @@
         <v>100</v>
       </c>
       <c r="T33">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="U33">
         <v>100</v>
@@ -5771,7 +5726,7 @@
         <v>100</v>
       </c>
       <c r="I34">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J34">
         <v>100</v>
@@ -5783,7 +5738,7 @@
         <v>100</v>
       </c>
       <c r="M34">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="N34">
         <v>100</v>
@@ -5792,7 +5747,7 @@
         <v>100</v>
       </c>
       <c r="P34">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q34">
         <v>100</v>
@@ -5804,7 +5759,7 @@
         <v>100</v>
       </c>
       <c r="T34">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="U34">
         <v>100</v>
@@ -5876,19 +5831,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2">
-        <v>61.3</v>
+        <v>67.7</v>
       </c>
       <c r="G2" s="2">
-        <v>38.7</v>
+        <v>32.3</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5908,19 +5863,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
-        <v>87.09999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>12.9</v>
+        <v>16.1</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5931,7 +5886,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -5940,19 +5895,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>90.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>9.699999999999999</v>
+        <v>16.1</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5963,7 +5918,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -5972,19 +5927,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>93.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>6.5</v>
+        <v>12.9</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5995,7 +5950,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>60</v>
@@ -6004,19 +5959,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>100</v>
+        <v>93.5</v>
       </c>
       <c r="G6" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6027,7 +5982,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>61</v>
@@ -6036,16 +5991,16 @@
         <v>31</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="G7" s="2">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H7">
         <v>8.1</v>
@@ -6080,7 +6035,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6130,7 +6085,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6168,10 +6123,10 @@
         <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6191,10 +6146,10 @@
         <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -6208,16 +6163,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920036</v>
+        <v>22330051920043</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -6231,22 +6186,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920036</v>
+        <v>22330051920043</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6254,16 +6209,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920038</v>
+        <v>22330051920036</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -6277,22 +6232,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920038</v>
+        <v>22330051920331</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6300,22 +6255,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920189</v>
+        <v>22330051920191</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6323,22 +6278,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920189</v>
+        <v>22330051920327</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6346,16 +6301,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920043</v>
+        <v>22330051920051</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -6364,213 +6319,6 @@
         <v>56</v>
       </c>
       <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920043</v>
-      </c>
-      <c r="B11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" t="s">
-        <v>94</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920049</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920049</v>
-      </c>
-      <c r="B13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" t="s">
-        <v>83</v>
-      </c>
-      <c r="D13" t="s">
-        <v>95</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920031</v>
-      </c>
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D14" t="s">
-        <v>96</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920331</v>
-      </c>
-      <c r="B15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" t="s">
-        <v>85</v>
-      </c>
-      <c r="D15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920191</v>
-      </c>
-      <c r="B16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>56</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920042</v>
-      </c>
-      <c r="B17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" t="s">
-        <v>87</v>
-      </c>
-      <c r="D17" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920327</v>
-      </c>
-      <c r="B18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" t="s">
-        <v>88</v>
-      </c>
-      <c r="D18" t="s">
-        <v>100</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>56</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920051</v>
-      </c>
-      <c r="B19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D19" t="s">
-        <v>101</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>56</v>
-      </c>
-      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4BEM - Estadisticos 20232.xlsx
+++ b/grupos/4BEM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="85">
   <si>
     <t>Materia</t>
   </si>
@@ -191,21 +191,21 @@
     <t>Sanchez Morales Gilberto</t>
   </si>
   <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
+    <t>Faltante Faltante Faltante</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>Hernández Castro Enrique</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
-    <t>Faltante Faltante Faltante</t>
-  </si>
-  <si>
-    <t>Hernández Castro Enrique</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
     <t>Flores Paz Victor</t>
   </si>
   <si>
@@ -221,64 +221,58 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>CRUZ</t>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>JENKINS</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>GIL</t>
   </si>
   <si>
     <t>PALOMINO</t>
   </si>
   <si>
-    <t>GIL</t>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ACOSTA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>MELCHOR</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>CARLOS YAEL</t>
+    <t>MIGUEL ANTONIO</t>
+  </si>
+  <si>
+    <t>ARTHUR RICHARD</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>JOSE RAUL</t>
   </si>
   <si>
     <t>AARON MIGUEL</t>
   </si>
   <si>
-    <t>JOSE RAUL</t>
-  </si>
-  <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
     <t>JORGE IVAN</t>
-  </si>
-  <si>
-    <t>GEOVANNI</t>
   </si>
 </sst>
 </file>
@@ -826,22 +820,22 @@
         <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>-1</v>
@@ -862,7 +856,7 @@
         <v>9</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC4">
         <v>8</v>
@@ -915,22 +909,22 @@
         <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
         <v>-1</v>
@@ -951,7 +945,7 @@
         <v>10</v>
       </c>
       <c r="AB5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC5">
         <v>10</v>
@@ -1004,37 +998,37 @@
         <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V6">
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA6">
         <v>7</v>
@@ -1093,22 +1087,22 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>-1</v>
@@ -1182,22 +1176,22 @@
         <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>-1</v>
@@ -1271,22 +1265,22 @@
         <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>-1</v>
@@ -1360,43 +1354,43 @@
         <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>7</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC10">
         <v>9</v>
@@ -1449,34 +1443,34 @@
         <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z11">
         <v>7</v>
@@ -1485,7 +1479,7 @@
         <v>9</v>
       </c>
       <c r="AB11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC11">
         <v>10</v>
@@ -1538,28 +1532,28 @@
         <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -1568,13 +1562,13 @@
         <v>8</v>
       </c>
       <c r="Z12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA12">
         <v>8</v>
       </c>
       <c r="AB12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC12">
         <v>9</v>
@@ -1627,43 +1621,43 @@
         <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA13">
         <v>8</v>
       </c>
       <c r="AB13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC13">
         <v>8</v>
@@ -1716,22 +1710,22 @@
         <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>-1</v>
@@ -1740,19 +1734,19 @@
         <v>6</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>9</v>
       </c>
       <c r="Z14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC14">
         <v>8</v>
@@ -1805,28 +1799,28 @@
         <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1838,10 +1832,10 @@
         <v>7</v>
       </c>
       <c r="AA15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC15">
         <v>7</v>
@@ -1894,22 +1888,22 @@
         <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>-1</v>
@@ -1918,13 +1912,13 @@
         <v>5</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA16">
         <v>6</v>
@@ -1983,22 +1977,22 @@
         <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>-1</v>
@@ -2010,16 +2004,16 @@
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z17">
         <v>6</v>
       </c>
       <c r="AA17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC17">
         <v>5</v>
@@ -2072,28 +2066,28 @@
         <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>8</v>
@@ -2105,10 +2099,10 @@
         <v>10</v>
       </c>
       <c r="AA18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC18">
         <v>7</v>
@@ -2161,43 +2155,43 @@
         <v>6</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>9</v>
       </c>
       <c r="Z19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA19">
         <v>7</v>
       </c>
       <c r="AB19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC19">
         <v>7</v>
@@ -2250,28 +2244,28 @@
         <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>10</v>
@@ -2339,22 +2333,22 @@
         <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>-1</v>
@@ -2363,7 +2357,7 @@
         <v>6</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2375,7 +2369,7 @@
         <v>8</v>
       </c>
       <c r="AB21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC21">
         <v>8</v>
@@ -2428,22 +2422,22 @@
         <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>-1</v>
@@ -2452,16 +2446,16 @@
         <v>5</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB22">
         <v>6</v>
@@ -2517,22 +2511,22 @@
         <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>-1</v>
@@ -2541,16 +2535,16 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z23">
         <v>7</v>
       </c>
       <c r="AA23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>7</v>
@@ -2606,22 +2600,22 @@
         <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V24">
         <v>-1</v>
@@ -2630,16 +2624,16 @@
         <v>5</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>5</v>
       </c>
       <c r="Z24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB24">
         <v>5</v>
@@ -2695,22 +2689,22 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V25">
         <v>-1</v>
@@ -2722,7 +2716,7 @@
         <v>8</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z25">
         <v>8</v>
@@ -2731,7 +2725,7 @@
         <v>8</v>
       </c>
       <c r="AB25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC25">
         <v>10</v>
@@ -2784,22 +2778,22 @@
         <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>-1</v>
@@ -2873,28 +2867,28 @@
         <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>8</v>
@@ -2903,7 +2897,7 @@
         <v>10</v>
       </c>
       <c r="Z27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA27">
         <v>9</v>
@@ -2962,22 +2956,22 @@
         <v>6</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V28">
         <v>-1</v>
@@ -2995,10 +2989,10 @@
         <v>7</v>
       </c>
       <c r="AA28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC28">
         <v>7</v>
@@ -3051,22 +3045,22 @@
         <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V29">
         <v>-1</v>
@@ -3087,7 +3081,7 @@
         <v>8</v>
       </c>
       <c r="AB29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC29">
         <v>9</v>
@@ -3140,28 +3134,28 @@
         <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V30">
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>8</v>
@@ -3170,7 +3164,7 @@
         <v>9</v>
       </c>
       <c r="Z30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA30">
         <v>9</v>
@@ -3229,43 +3223,43 @@
         <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>6</v>
       </c>
       <c r="Z31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC31">
         <v>6</v>
@@ -3318,22 +3312,22 @@
         <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V32">
         <v>-1</v>
@@ -3354,7 +3348,7 @@
         <v>9</v>
       </c>
       <c r="AB32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC32">
         <v>9</v>
@@ -3407,22 +3401,22 @@
         <v>8</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V33">
         <v>-1</v>
@@ -3434,16 +3428,16 @@
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z33">
         <v>10</v>
       </c>
       <c r="AA33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC33">
         <v>9</v>
@@ -3496,34 +3490,34 @@
         <v>6</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V34">
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z34">
         <v>10</v>
@@ -3719,7 +3713,7 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="U4">
         <v>100</v>
@@ -3849,13 +3843,13 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S6">
         <v>100</v>
       </c>
       <c r="T6">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U6">
         <v>100</v>
@@ -3911,7 +3905,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -3923,7 +3917,7 @@
         <v>100</v>
       </c>
       <c r="T7">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="U7">
         <v>100</v>
@@ -4059,7 +4053,7 @@
         <v>100</v>
       </c>
       <c r="T9">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="U9">
         <v>100</v>
@@ -4127,7 +4121,7 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="U10">
         <v>100</v>
@@ -4183,19 +4177,19 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="Q11">
         <v>100</v>
       </c>
       <c r="R11">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S11">
         <v>100</v>
       </c>
       <c r="T11">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="U11">
         <v>100</v>
@@ -4251,19 +4245,19 @@
         <v>100</v>
       </c>
       <c r="P12">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="Q12">
+        <v>100</v>
+      </c>
+      <c r="R12">
+        <v>100</v>
+      </c>
+      <c r="S12">
+        <v>100</v>
+      </c>
+      <c r="T12">
         <v>95</v>
-      </c>
-      <c r="Q12">
-        <v>100</v>
-      </c>
-      <c r="R12">
-        <v>100</v>
-      </c>
-      <c r="S12">
-        <v>100</v>
-      </c>
-      <c r="T12">
-        <v>92</v>
       </c>
       <c r="U12">
         <v>100</v>
@@ -4319,7 +4313,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -4331,7 +4325,7 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -4399,7 +4393,7 @@
         <v>100</v>
       </c>
       <c r="T14">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="U14">
         <v>100</v>
@@ -4455,19 +4449,19 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q15">
         <v>100</v>
       </c>
       <c r="R15">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S15">
         <v>100</v>
       </c>
       <c r="T15">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="U15">
         <v>100</v>
@@ -4523,19 +4517,19 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="Q16">
         <v>100</v>
       </c>
       <c r="R16">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S16">
         <v>100</v>
       </c>
       <c r="T16">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -4597,13 +4591,13 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="S17">
         <v>100</v>
       </c>
       <c r="T17">
-        <v>98</v>
+        <v>93.8</v>
       </c>
       <c r="U17">
         <v>100</v>
@@ -4727,7 +4721,7 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -4739,7 +4733,7 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>94</v>
+        <v>91.3</v>
       </c>
       <c r="U19">
         <v>100</v>
@@ -4875,7 +4869,7 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="U21">
         <v>100</v>
@@ -4931,7 +4925,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -4943,7 +4937,7 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="U22">
         <v>100</v>
@@ -4999,19 +4993,19 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="Q23">
         <v>100</v>
       </c>
       <c r="R23">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S23">
         <v>100</v>
       </c>
       <c r="T23">
-        <v>90</v>
+        <v>91.3</v>
       </c>
       <c r="U23">
         <v>100</v>
@@ -5067,19 +5061,19 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="Q24">
         <v>100</v>
       </c>
       <c r="R24">
-        <v>88.59999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S24">
         <v>100</v>
       </c>
       <c r="T24">
-        <v>98</v>
+        <v>93.8</v>
       </c>
       <c r="U24">
         <v>100</v>
@@ -5147,7 +5141,7 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>92</v>
+        <v>91.3</v>
       </c>
       <c r="U25">
         <v>100</v>
@@ -5283,7 +5277,7 @@
         <v>100</v>
       </c>
       <c r="T27">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="U27">
         <v>100</v>
@@ -5339,7 +5333,7 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -5351,7 +5345,7 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>96</v>
+        <v>91.3</v>
       </c>
       <c r="U28">
         <v>100</v>
@@ -5419,7 +5413,7 @@
         <v>100</v>
       </c>
       <c r="T29">
-        <v>94</v>
+        <v>93.8</v>
       </c>
       <c r="U29">
         <v>100</v>
@@ -5475,19 +5469,19 @@
         <v>100</v>
       </c>
       <c r="P30">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="Q30">
+        <v>100</v>
+      </c>
+      <c r="R30">
+        <v>100</v>
+      </c>
+      <c r="S30">
+        <v>100</v>
+      </c>
+      <c r="T30">
         <v>95</v>
-      </c>
-      <c r="Q30">
-        <v>100</v>
-      </c>
-      <c r="R30">
-        <v>100</v>
-      </c>
-      <c r="S30">
-        <v>100</v>
-      </c>
-      <c r="T30">
-        <v>92</v>
       </c>
       <c r="U30">
         <v>100</v>
@@ -5543,19 +5537,19 @@
         <v>100</v>
       </c>
       <c r="P31">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="Q31">
+        <v>100</v>
+      </c>
+      <c r="R31">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="S31">
+        <v>100</v>
+      </c>
+      <c r="T31">
         <v>85</v>
-      </c>
-      <c r="Q31">
-        <v>100</v>
-      </c>
-      <c r="R31">
-        <v>95.5</v>
-      </c>
-      <c r="S31">
-        <v>100</v>
-      </c>
-      <c r="T31">
-        <v>80</v>
       </c>
       <c r="U31">
         <v>100</v>
@@ -5623,7 +5617,7 @@
         <v>100</v>
       </c>
       <c r="T32">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="U32">
         <v>100</v>
@@ -5679,7 +5673,7 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="Q33">
         <v>100</v>
@@ -5691,7 +5685,7 @@
         <v>100</v>
       </c>
       <c r="T33">
-        <v>82</v>
+        <v>88.8</v>
       </c>
       <c r="U33">
         <v>100</v>
@@ -5747,7 +5741,7 @@
         <v>100</v>
       </c>
       <c r="P34">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q34">
         <v>100</v>
@@ -5759,7 +5753,7 @@
         <v>100</v>
       </c>
       <c r="T34">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="U34">
         <v>100</v>
@@ -5831,19 +5825,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>67.7</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>32.3</v>
+        <v>12.9</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5854,7 +5848,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -5863,19 +5857,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>83.90000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="G3" s="2">
-        <v>16.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5895,19 +5889,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>83.90000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="G4" s="2">
-        <v>16.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5918,7 +5912,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -5927,19 +5921,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>87.09999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="G5" s="2">
-        <v>12.9</v>
+        <v>6.5</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5950,7 +5944,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>60</v>
@@ -5959,19 +5953,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>93.5</v>
+        <v>96.8</v>
       </c>
       <c r="G6" s="2">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5982,7 +5976,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>61</v>
@@ -5991,19 +5985,19 @@
         <v>31</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6035,7 +6029,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6085,7 +6079,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6117,16 +6111,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920034</v>
+        <v>22330051920038</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6140,22 +6134,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920034</v>
+        <v>22330051920038</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6163,22 +6157,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920043</v>
+        <v>22330051920189</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6186,22 +6180,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920043</v>
+        <v>22330051920189</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6209,7 +6203,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920036</v>
+        <v>22330051920031</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
@@ -6218,13 +6212,13 @@
         <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6232,7 +6226,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920331</v>
+        <v>22330051920036</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
@@ -6241,13 +6235,13 @@
         <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6255,7 +6249,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920191</v>
+        <v>22330051920043</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
@@ -6264,7 +6258,7 @@
         <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -6287,7 +6281,7 @@
         <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
         <v>5</v>
@@ -6296,29 +6290,6 @@
         <v>56</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920051</v>
-      </c>
-      <c r="B10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" t="s">
-        <v>86</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4BEM - Estadisticos 20232.xlsx
+++ b/grupos/4BEM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="85">
   <si>
     <t>Materia</t>
   </si>
@@ -197,18 +197,18 @@
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
+    <t>Hernández Castro Enrique</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Flores Paz Victor</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Hernández Castro Enrique</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Flores Paz Victor</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -224,15 +224,15 @@
     <t>HERRERA</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
     <t>JENKINS</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
     <t>PALOMINO</t>
   </si>
   <si>
@@ -242,15 +242,15 @@
     <t>ACOSTA</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -260,13 +260,13 @@
     <t>MIGUEL ANTONIO</t>
   </si>
   <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>JOSE RAUL</t>
+  </si>
+  <si>
     <t>ARTHUR RICHARD</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>JOSE RAUL</t>
   </si>
   <si>
     <t>AARON MIGUEL</t>
@@ -838,7 +838,7 @@
         <v>6</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>7</v>
@@ -927,7 +927,7 @@
         <v>10</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -948,7 +948,7 @@
         <v>9</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1016,7 +1016,7 @@
         <v>5</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -1105,7 +1105,7 @@
         <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -1194,7 +1194,7 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -1283,7 +1283,7 @@
         <v>7</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W9">
         <v>7</v>
@@ -1304,7 +1304,7 @@
         <v>7</v>
       </c>
       <c r="AC9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1372,7 +1372,7 @@
         <v>6</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W10">
         <v>6</v>
@@ -1393,7 +1393,7 @@
         <v>7</v>
       </c>
       <c r="AC10">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1461,7 +1461,7 @@
         <v>7</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -1550,7 +1550,7 @@
         <v>5</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>7</v>
@@ -1571,7 +1571,7 @@
         <v>8</v>
       </c>
       <c r="AC12">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1639,7 +1639,7 @@
         <v>6</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>6</v>
@@ -1728,7 +1728,7 @@
         <v>6</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>6</v>
@@ -1817,7 +1817,7 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>6</v>
@@ -1838,7 +1838,7 @@
         <v>7</v>
       </c>
       <c r="AC15">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1906,7 +1906,7 @@
         <v>6</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>5</v>
@@ -1995,7 +1995,7 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -2016,7 +2016,7 @@
         <v>6</v>
       </c>
       <c r="AC17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2084,7 +2084,7 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -2173,7 +2173,7 @@
         <v>6</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>6</v>
@@ -2262,7 +2262,7 @@
         <v>8</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>8</v>
@@ -2351,7 +2351,7 @@
         <v>6</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>6</v>
@@ -2440,7 +2440,7 @@
         <v>6</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>5</v>
@@ -2529,7 +2529,7 @@
         <v>6</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>5</v>
@@ -2618,7 +2618,7 @@
         <v>6</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>5</v>
@@ -2639,7 +2639,7 @@
         <v>5</v>
       </c>
       <c r="AC24">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2707,7 +2707,7 @@
         <v>5</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W25">
         <v>7</v>
@@ -2796,7 +2796,7 @@
         <v>8</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>6</v>
@@ -2817,7 +2817,7 @@
         <v>8</v>
       </c>
       <c r="AC26">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2885,7 +2885,7 @@
         <v>8</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>6</v>
@@ -2974,7 +2974,7 @@
         <v>6</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>6</v>
@@ -2995,7 +2995,7 @@
         <v>6</v>
       </c>
       <c r="AC28">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3063,7 +3063,7 @@
         <v>6</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W29">
         <v>6</v>
@@ -3152,7 +3152,7 @@
         <v>6</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>7</v>
@@ -3173,7 +3173,7 @@
         <v>7</v>
       </c>
       <c r="AC30">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3241,7 +3241,7 @@
         <v>7</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W31">
         <v>6</v>
@@ -3330,7 +3330,7 @@
         <v>6</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W32">
         <v>6</v>
@@ -3419,7 +3419,7 @@
         <v>7</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>7</v>
@@ -3440,7 +3440,7 @@
         <v>7</v>
       </c>
       <c r="AC33">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3508,7 +3508,7 @@
         <v>6</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W34">
         <v>6</v>
@@ -3529,7 +3529,7 @@
         <v>7</v>
       </c>
       <c r="AC34">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5912,7 +5912,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -5921,19 +5921,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>93.5</v>
+        <v>96.8</v>
       </c>
       <c r="G5" s="2">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>60</v>
@@ -5953,19 +5953,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5976,7 +5976,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>61</v>
@@ -5997,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6008,7 +6008,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>62</v>
@@ -6029,7 +6029,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6079,7 +6079,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6157,7 +6157,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920189</v>
+        <v>22330051920031</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
@@ -6169,10 +6169,10 @@
         <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6180,22 +6180,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920189</v>
+        <v>22330051920036</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6203,22 +6203,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920031</v>
+        <v>22330051920189</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6226,22 +6226,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920036</v>
+        <v>22330051920043</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6249,16 +6249,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920043</v>
+        <v>22330051920327</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -6267,29 +6267,6 @@
         <v>56</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920327</v>
-      </c>
-      <c r="B9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>
